--- a/output/casestudy_20260911.xlsx
+++ b/output/casestudy_20260911.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.789551900000333</v>
+        <v>10.48129130000052</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.64612120000038</v>
+        <v>10.69720949999828</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.389636599999903</v>
+        <v>6.614849899999172</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.85267900000008</v>
+        <v>11.14252639999904</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.59487510000008</v>
+        <v>12.34940760000063</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>8.159642600000097</v>
+        <v>9.825606699998389</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.966774600000008</v>
+        <v>12.4248733000004</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>10.52072090000001</v>
+        <v>13.06266490000053</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>14.21970160000001</v>
+        <v>16.94996490000085</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.523279500000172</v>
+        <v>8.729260400001294</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6.112096100000144</v>
+        <v>7.51047490000019</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>10.5 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.6 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.4 초</t>
+          <t>6.6 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.9 초</t>
+          <t>11.1 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.6 초</t>
+          <t>12.3 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8.2 초</t>
+          <t>9.8 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.0 초</t>
+          <t>12.4 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.5 초</t>
+          <t>13.1 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14.2 초</t>
+          <t>16.9 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.5 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6.1 초</t>
+          <t>7.5 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>110.0 초</t>
+          <t>128.3 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260911.xlsx
+++ b/output/casestudy_20260911.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>10.48129130000052</v>
+        <v>10.10994440000104</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.69720949999828</v>
+        <v>10.17372369999975</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.614849899999172</v>
+        <v>6.519859299998643</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.14252639999904</v>
+        <v>10.71794500000033</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>12.34940760000063</v>
+        <v>11.78283040000133</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.825606699998389</v>
+        <v>8.721836599999733</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>12.4248733000004</v>
+        <v>10.71023080000123</v>
       </c>
     </row>
     <row r="9">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>13.06266490000053</v>
+        <v>11.3815838999999</v>
       </c>
     </row>
     <row r="10">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>16.94996490000085</v>
+        <v>14.92818049999914</v>
       </c>
     </row>
     <row r="11">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>8.729260400001294</v>
+        <v>7.716307200000301</v>
       </c>
     </row>
     <row r="12">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>7.51047490000019</v>
+        <v>6.468969099998503</v>
       </c>
     </row>
   </sheetData>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.5 초</t>
+          <t>10.1 초</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14010,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>10.2 초</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.6 초</t>
+          <t>6.5 초</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.1 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.3 초</t>
+          <t>11.8 초</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9.8 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.4 초</t>
+          <t>10.7 초</t>
         </is>
       </c>
     </row>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.1 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16.9 초</t>
+          <t>14.9 초</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8.7 초</t>
+          <t>7.7 초</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7.5 초</t>
+          <t>6.5 초</t>
         </is>
       </c>
     </row>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>128.3 초</t>
+          <t>116.7 초</t>
         </is>
       </c>
     </row>
